--- a/outputs/38537.xlsx
+++ b/outputs/38537.xlsx
@@ -229,36 +229,40 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -515,471 +519,471 @@
   <dimension ref="A1:Q36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="10.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="10.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="10.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="10.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="str">
+      <c r="A3" s="5" t="str">
         <f aca="false">IF(B3="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B3)+9,"000"))</f>
         <v/>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="6"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="1"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="7"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="str">
+      <c r="A4" s="5" t="str">
         <f aca="false">IF(B4="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B4)+9,"000"))</f>
         <v/>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="6"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="1"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="str">
+      <c r="A5" s="5" t="str">
         <f aca="false">IF(B5="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B5)+9,"000"))</f>
         <v/>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="6"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="1"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="7"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="str">
+      <c r="A6" s="5" t="str">
         <f aca="false">IF(B6="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B6)+9,"000"))</f>
         <v/>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="6"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="1"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="str">
+      <c r="A7" s="5" t="str">
         <f aca="false">IF(B7="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B7)+9,"000"))</f>
         <v/>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="1"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="str">
+      <c r="A8" s="5" t="str">
         <f aca="false">IF(B8="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B8)+9,"000"))</f>
         <v>ABC123-02-010</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="1"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="str">
+      <c r="A9" s="5" t="str">
         <f aca="false">IF(B9="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B9)+9,"000"))</f>
         <v>ABC123-02-011</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="I9" s="7"/>
-      <c r="J9" s="1"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="str">
+      <c r="A10" s="5" t="str">
         <f aca="false">IF(B10="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B10)+9,"000"))</f>
         <v>ABC123-02-012</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I10" s="7"/>
-      <c r="J10" s="1"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="str">
+      <c r="A11" s="5" t="str">
         <f aca="false">IF(B11="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B11)+9,"000"))</f>
         <v>ABC123-02-013</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I11" s="7"/>
-      <c r="J11" s="1"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="str">
+      <c r="A12" s="5" t="str">
         <f aca="false">IF(B12="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B12)+9,"000"))</f>
         <v>ABC123-02-014</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="1"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="str">
+      <c r="A13" s="5" t="str">
         <f aca="false">IF(B13="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B13)+9,"000"))</f>
         <v>ABC123-02-015</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="1"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="str">
+      <c r="A14" s="5" t="str">
         <f aca="false">IF(B14="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B14)+9,"000"))</f>
         <v>ABC123-02-016</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I14" s="7"/>
-      <c r="J14" s="1"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="str">
+      <c r="A15" s="5" t="str">
         <f aca="false">IF(B15="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B15)+9,"000"))</f>
         <v>ABC123-02-017</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I15" s="7"/>
-      <c r="J15" s="1"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="str">
+      <c r="A16" s="5" t="str">
         <f aca="false">IF(B16="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B16)+9,"000"))</f>
         <v/>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="6"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="1"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="7"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="str">
+      <c r="A17" s="5" t="str">
         <f aca="false">IF(B17="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B17)+9,"000"))</f>
         <v/>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="6"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="1"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="7"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="str">
+      <c r="A18" s="5" t="str">
         <f aca="false">IF(B18="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B18)+9,"000"))</f>
         <v>ABC123-02-018</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I18" s="7"/>
-      <c r="J18" s="1"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="str">
+      <c r="A19" s="5" t="str">
         <f aca="false">IF(B19="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B19)+9,"000"))</f>
         <v>ABC123-02-019</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="I19" s="7"/>
-      <c r="J19" s="1"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="str">
+      <c r="A20" s="5" t="str">
         <f aca="false">IF(B20="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B20)+9,"000"))</f>
         <v>ABC123-02-020</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I20" s="7"/>
-      <c r="J20" s="1"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="str">
+      <c r="A21" s="5" t="str">
         <f aca="false">IF(B21="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B21)+9,"000"))</f>
         <v>ABC123-02-021</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I21" s="7"/>
-      <c r="J21" s="1"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="str">
+      <c r="A22" s="5" t="str">
         <f aca="false">IF(B22="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B22)+9,"000"))</f>
         <v/>
       </c>
-      <c r="I22" s="7"/>
-      <c r="J22" s="1"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="str">
+      <c r="A23" s="5" t="str">
         <f aca="false">IF(B23="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B23)+9,"000"))</f>
         <v>ABC123-02-022</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I23" s="7"/>
-      <c r="J23" s="1"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="str">
+      <c r="A24" s="5" t="str">
         <f aca="false">IF(B24="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B24)+9,"000"))</f>
         <v>ABC123-02-023</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I24" s="7"/>
-      <c r="J24" s="1"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="str">
+      <c r="A25" s="5" t="str">
         <f aca="false">IF(B25="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B25)+9,"000"))</f>
         <v/>
       </c>
-      <c r="I25" s="7"/>
-      <c r="J25" s="1"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="str">
+      <c r="A26" s="5" t="str">
         <f aca="false">IF(B26="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B26)+9,"000"))</f>
         <v/>
       </c>
-      <c r="I26" s="7"/>
-      <c r="J26" s="1"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="str">
+      <c r="A27" s="5" t="str">
         <f aca="false">IF(B27="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B27)+9,"000"))</f>
         <v/>
       </c>
-      <c r="I27" s="7"/>
-      <c r="J27" s="1"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="str">
+      <c r="A28" s="5" t="str">
         <f aca="false">IF(B28="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B28)+9,"000"))</f>
         <v>ABC123-02-024</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I28" s="7"/>
-      <c r="J28" s="1"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="str">
+      <c r="A29" s="5" t="str">
         <f aca="false">IF(B29="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B29)+9,"000"))</f>
         <v>ABC123-02-025</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I29" s="7"/>
-      <c r="J29" s="1"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="str">
+      <c r="A30" s="5" t="str">
         <f aca="false">IF(B30="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B30)+9,"000"))</f>
         <v/>
       </c>
-      <c r="I30" s="7"/>
-      <c r="J30" s="1"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="str">
+      <c r="A31" s="5" t="str">
         <f aca="false">IF(B31="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B31)+9,"000"))</f>
         <v/>
       </c>
-      <c r="I31" s="7"/>
-      <c r="J31" s="1"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="str">
+      <c r="A32" s="5" t="str">
         <f aca="false">IF(B32="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B32)+9,"000"))</f>
         <v>ABC123-02-026</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="F32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I32" s="7"/>
-      <c r="J32" s="1"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="str">
+      <c r="A33" s="5" t="str">
         <f aca="false">IF(B33="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B33)+9,"000"))</f>
         <v/>
       </c>
-      <c r="I33" s="7"/>
-      <c r="J33" s="1"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="str">
+      <c r="A34" s="5" t="str">
         <f aca="false">IF(B34="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B34)+9,"000"))</f>
         <v>ABC123-02-027</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I34" s="7"/>
-      <c r="J34" s="1"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="str">
+      <c r="A35" s="5" t="str">
         <f aca="false">IF(B35="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B35)+9,"000"))</f>
         <v/>
       </c>
-      <c r="I35" s="7"/>
-      <c r="J35" s="1"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="str">
+      <c r="A36" s="5" t="str">
         <f aca="false">IF(B36="","",$B$2&amp;"-02-"&amp;TEXT(COUNTA($B$3:B36)+9,"000"))</f>
         <v>ABC123-02-028</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I36" s="7"/>
-      <c r="J36" s="1"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
